--- a/04_DESIGN_TABLES/DesignTable_2611_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2611_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF3"/>
+  <dimension ref="A1:BF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,204 @@
       <c r="BF3" t="inlineStr">
         <is>
           <t>2611-08-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2611-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4715</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1851</v>
+      </c>
+      <c r="J4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="n">
+        <v>37</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2043</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.51241</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2611-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Male Run x Female Branch Tee, 1 1/16-12 JIC x 3/4-14 NPTF x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] 2026-10-02 new master (JIC-TEES): legs / hex / bores from the OMi dimension file (OMi M 1 / M 2 / L 1 / Hex Flat / Side 1 ID / Side 2 ID = JIC leg / male pipe leg / female pipe branch leg / body hex / JIC bore / male pipe bore (Brennan TFA catalog p52 drawing M / L / L1 / Y / B1 / A2; Brennan 2611-06-06-06-FG STEP: 1.310 / 1.220 / 1.020, A/F 0.875, bores 0.297 / 0.406 = OMi row 885)); OMi = Brennan data (Brennan catalog TFA p52 (MJ-MP-FP TEE) prints the same values) = ONE source -&gt; ASSUMED; thread majors from the OMi thread callouts; female port tap drill / thread length: NO source yet (Q-TRANSFER-TAPDRILL) | previous: OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 2611-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M1@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "M LGTH" = "1.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the B1 JIC tip (column mapping: REPORT.md, table 2611); N5@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "L LGTH" = "1.590" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the A2 male NPTF tip (column mapping: REPORT.md, table 2611); N1@DRIVE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "L1 LGTH" = "1.360" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - axis to the A3 female NPTF port face (column mapping: REPORT.md, table 2611); Y1@HEX: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2611); D@BORE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - JIC drill (column mapping: REPORT.md, table 2611); D1@BORE: Brennan TFA catalog p.52 table TFA-p052-t03 "2611-FG MJ-MP-FP TEE" row 2611-12-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 675.8, page verified True) [Brennan = yes 2026-10-18] - male NPTF drill (column mapping: REPORT.md, table 2611); TAPDRILL@BORE: end library: tap drill of the -12 female NPTF port = 0.91 (gen_straight2 FPT[12] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-TRANSFER-ENDLIB yes 2026-10-08: tap drills from the end library; = A1 YES 2026-10-18] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; male NPTF legs: ASME B1.20.3 cone + relief to the Brennan-measured 5404 end length; confirmed on a forged tee by Brennan 5600-16-16-16-FG STEP (hex stops at N - 0.94, relief dia 1.315 = pipe OD, 0.001 proud of the 1.3125 flats); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries = Air-Way's per-size value; user 2026-10-08 'reuse end details - yes'), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only); the row's PORTDEPTH only where the row carries one - said in $COMMENT); connecting drill to the axis crossing = the tap drill carried to the crossing (MEASURED: Brennan 2611-06-06-06-FG STEP - the 0.578 drill runs from the bottom of the 0.58 deep tapered port to the run axis; the tapered port itself and its 45deg mouth chamfer are drawn as the tap-drill cylinder + the Thread feature, as on every built female port); each leg bore runs from its face to the axis crossing; Brennan 2611-06-06-06-FG STEP (2026-10-02, tools/measure/forged.py): run hex bar from the JIC hex face (0.754 = M - the 2403 -06 JIC end length 0.556) through the crossing to the male pipe hex face (0.660 = N - the 5404 -06 end length 0.56), branch hex arm to the female collar (0.760), collar 0.260 long at the flats dia, A/F 0.875, flats normal to Z, bores 0.297 / 0.406 from each face to the crossing = this pattern; JIC end = the 2403 -06 chain but with NO thread relief on the STEP (model keeps the MS33656J relief, ASSUMPTION as on every built tee); male pipe end: STEP taper 0.4817 from a 45deg tip chamfer + a 0.028 relief at the pipe OD 0.675, model = ASME B1.20.3 cone + relief (library, as every built male pipe leg) with the same end length 0.56</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2026-10-02 (JIC-TEES): stays MISSING - OMi gives no body dimensions for this part (M1@DRIVE, N5@DRIVE, N1@DRIVE, Y1@HEX, D@BORE, D1@BORE); the Brennan catalog TFA p52 (MJ-MP-FP TEE) prints them, but a Brennan-only value is not filled until Q-BRENNAN-ONLY is answered (proposals/); also no female-port tap drill / thread length source | previous: BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 2611-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate) | leg 3: female port thread length = MS51503 P1 0.91 (library) - the row has no measured PORTDEPTH@BORE</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2611-12-12-12-FG</t>
         </is>
       </c>
     </row>
